--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_support_assessment.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_support_assessment.xlsx
@@ -1071,12 +1071,12 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0e8437f74f4806888e5591a96881eafbd93882034aeee5f95289e5e4e33ffd0e</t>
+          <t>e06d6b78de8553c4083d2c13294f938d3307ca56244695091c877cfa0bf3c4b5</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>eff2c499a5c4940dc21ce73744286fd11e3e6625c24f5435a8894c1636226c2f</t>
+          <t>de6ec81f1a945bd905f86fc6989bd3221a7d44172039a80ac36ba3543c6d21c9</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>03e62822ec749f26f75531fda29901e01b2df9a6b8cb7cb4c50a6df468002a43</t>
+          <t>ee785385f6f609497bb4b3846b87df88a8369b8f66372da49c48208c1e66296f</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>8472b7cb5866ae8b1b831d564aa4893fbc9feecc090e001918f9412e301e16f4</t>
+          <t>3e9a0aae47d14c8022ce0449c559a3aff8a0ca942716e6f43101c14f3327df79</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>cbabb701585daaae6b34523e257042e5d9d35efc87301337c2983e009aaf3fc7</t>
+          <t>38d5b86c1609246fc5d9d80537aff4b1add5ec73cd372defe47195c02987b73b</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>593153a758540b137762bea004366e87ad5f1b098d055f7a19522ffdda30aebf</t>
+          <t>61791e1d60eb9833720547a365caf250cde6a138bca568ae0f888d33fa328dbc</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>e666d25190bd8d6bda1d599609016dd5e10ec225f4cede39c1e3ccb3ac58addc</t>
+          <t>95150a5cdcf70d9c15f3fef9f11ff1b0d324b35f9861b143c98a02cd8f241258</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>15e421fba25124b4a7f23b807e1f131c0f9344f0cfcf760cd4542c6c7499626f</t>
+          <t>f857e9e0986a58b0ea3e4873b4946cac42d808f8a5c0bd2cc7016a5e338a7891</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>f50c1654eb569c1d9b71a5b7bf5f7eb0d24fa423b6c9bb26dc85f54b8978b6bb</t>
+          <t>711022e261450791aa3c3058965cf0f5a26ed8004f11705ca5d8c19aa016c907</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3baac6c1c10d34f1d9e25d4d400fb39df44f655d00fb29fb34757db3125de4e8</t>
+          <t>4183b357edfaadad060d2bd75a523baf21855e33b8c87b0ec512f0bf21aa3d49</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>a9903b04ffa0f628ad6ab39a47d1d387429fae7ab2eb5dbceee06f830c8350ee</t>
+          <t>63bbefa95e33203fdd463c76494235f88c617652c90ee30f870f7e9101c9985c</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>263bfadfcbe429de0725090bec2a84698edebf5ef5f961739931676e7093371f</t>
+          <t>64f94cbb427da8c5bbba4107d494eb6c3c52566c21d9e9b757cd3c0ff5a2ba8d</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>42d56bcea47bb4a0162e25dba879f3578eb1ad50390ab5da991cba8da55cc6bc</t>
+          <t>8de3b9929c603de6bc2bdf87fa442f17848f729a85e071e8a53ad144401ed669</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>fdf15d167313087a0346f998820820506b156c14b8fb96114ab0e9f215dca620</t>
+          <t>7022025be010b11a0cad9c511c236ff167f9a5ebc44c57b7ba1e58bc22f42856</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>80444e7ff4fdc228c3e46ccb3807e3686171400aa550ddcc4a4eb62f14de76a4</t>
+          <t>7e884b07c74f4528a855c8f3ec118f1ec599ea7ce36766827914e1d998a492a8</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>0748b1b6bff927d541e36d03c668da525c8afc660104b48e4fb2ac067b065bae</t>
+          <t>5b395f54d94d19f696f836e39fff6db513321874296951418ceb0ed0e97a33d5</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>84ae099186ce753e970e7878bf767020be562d1a61f28135fabfb2da43a63cf5</t>
+          <t>1423a797e84e82c6ded2c2ace2bd82e594977eddb59cedb963226aac1ee79196</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>ed0369f2d47f4e71db4acf26c8d916bf312017348ea85b0f95c0a1bc89b4616f</t>
+          <t>fe1faeb3ea8ddc3723a0d76cf2fd611a3bb902158fd5421d1413bc5ee1c8e925</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>331f8a1a3d7be6643f2ade3e0dc4a52af1bbe74a09f775d1c7d6cdd0b0ad9d56</t>
+          <t>74c428d4a28e7e4df0d5c60dcd4c352dabcd92bf8af640700527003eaa515871</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>f30cdd0ad6914e6455818d84e46b9ae658026c02cf01018b20e83ec84564414b</t>
+          <t>52e45ebf0de1fce33c5568aee96b97eb14c533e368cb3440e1e77d0d17e0291c</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4f377ee64dfe8fab15c10e90b3feec4c5e3871c676f8dd2cef1eb5773b337048</t>
+          <t>56c4091ffac8d2ffe4960f980a9883170bdf9144f95c2ee7dbbb5d41da945743</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>9e1588e842273d8ddc8740778c5fd5c88be2cf967ef128f0e9b6b563d56f4ca9</t>
+          <t>3a125119ea003e43e944608f2054aac219cea75a9aea9bc268ddd9a2ae8aee71</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>6ebae9926aae52b9ea28151103a71637ab7f3174a00bb189049d7d6d72fb1277</t>
+          <t>4b1a093f76ffe030efb6d61655391e858c0e977fbe7f5b07e70c7d18e10ea81d</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>e70e6953a2f7ea39acdee40160083a92bb015e2962aa7e3c37644a2c8e3f1c83</t>
+          <t>4ce4920b8a3208d72c0bc5cf24ec67de707858d2956550fc591a5961da73bc79</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>ec634eca8dc042fc54a1795f07438deb365552304eaa9d9792abfd4acb9bc42b</t>
+          <t>6e2556eb576f6636a0282f584bb97ea32a50c90791d73ef7a13dffb90ae7aa96</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>6bb5d268fd58ce566dc343968574434b1eb0448e3e382ab9492b4920aa927e9c</t>
+          <t>5f246ba8e5a5aa0796a57da27b67be366a7c8fda19730dab8f01f7279ad59a55</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>1e52009929f6f4a10b76fa58ffaa14670ebfb7638c0cdfc0a7c939133f2ec766</t>
+          <t>d80748f0d138ba5a0cb3cfb4f8ecf1f95528601a8c91a8ffc6ff385943f16624</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>d3e04efef9c07e1c53bd3c4a2348cb49082804e4dae4ff87825018da5a8ecc39</t>
+          <t>20b014037d13c3e7499ff7390dee82febd20c0da20a13b25c6c9666adeea74b3</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>62e7ea1ab69036130783e6dc5e3e117209f0116f7c90e2269fa2f010ec21d08b</t>
+          <t>065c27f98f9d2163c4d26dc2df34668dde2d457f68bf2e7ff7d91286368013e2</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>9326b6d552fc180d3eece2b92a467b59327bb82f704fa69eb47472e1a42c3926</t>
+          <t>324ffc625690e7d3404cf7030f9e7debda23f88c447c1be72e5305c9681a7bc0</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>fc65a233e51a4d4b8b99eba7a34a5b72b415d8dc2d5e6f519fd19e5fb688a11c</t>
+          <t>fed0ca5d16502bf78b5b5bb286fb756f4af876a1317124b273fa6e4c1a37377f</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -9069,12 +9069,12 @@
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>6d0b478791785e985c38d985888ca1d49251324dbb333513a1c28d697dcf4f9d</t>
+          <t>bd3e18cfb96bdc1dcf3c2e57338fbb382060d698e623e520b89b83c01cbe13c8</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>0500e8ca58cd7cb1dfdff300bdec41d357c9114cf57740283d8fb4333e4671b6</t>
+          <t>ce78bcad0fdc7cf0bffad684addac6bfbfccdfc0dcb01b2f5e7cd0d1a72ac641</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>1210dfb22b46457eb025258c4895f222fe925d283aa890d7851870c0b7fc6c49</t>
+          <t>934a87e7ca72ff416e4c722c71512d48b9001695c27d98d58e248c93b3497cea</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
@@ -9843,12 +9843,12 @@
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>d4ad094f31cf96146ad5464cb65e980982eb804acdad561009b446b979c4656f</t>
+          <t>6775808773e6a2a80f5584dc63999793bfd3b9e5f2ec92edd4a69d9c391381ec</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>d3f3e22ccec8a24f86709f6d4617768686e97a1be734595b933b6e5bb102b40b</t>
+          <t>e8f3d89da19f8123c89360d96d4f2a6a89029b9be3fe9ab228230d1d2c032f07</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>b6334d98d65d0916bdb29d1aed5ea0ba6ed9d5bafa8e4fc207378012d7d8a525</t>
+          <t>0644fbf754b5539468aeb8e17642ae401cfd9b95e54ffea9c99dcf9e227397fb</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>a69fe99e83f23460e9e6281fce64a2b55ecaed60ceb8115664a8cc51de0e61ee</t>
+          <t>b02a915913eea7c368198ae130d6472fb519ebc5df000f7fa338b4627a62e6cf</t>
         </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
@@ -10875,12 +10875,12 @@
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>61f5d7ef35dc11a2be1a84614a5423cce2d3dc0afd18cb0c1dde039851fb1884</t>
+          <t>75b4a52014cc050f7148415d2a2755f7b595d9689c6d617bf1ff01a3fb8fa6eb</t>
         </is>
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE40" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>f1ff1da733dfccf1942321a715701ed6d172ba7cfa54e2070239436518c503f4</t>
+          <t>c7cc91ecf5e2b7e06fc3760384034fddceb236b070cd44c3201a317c9654fdd7</t>
         </is>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE41" t="inlineStr">
@@ -11391,12 +11391,12 @@
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>099867dfb0f79cefe495f9a71682d1a51c3d3f991a11accbbaecd2dded16a48d</t>
+          <t>496e7a77402f966f429e0d61a36e30e9327c52617982bfa4cd51f57e1396f448</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>7d24cccb9f0c92100bf054ab8eae70343d73abdfbb574a42321e733a6fcd7f0d</t>
+          <t>d59c0d114903eeda3a8ae73f25ec6e1f9674e136ca79f9ffcc5f5f75f05fcf53</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>50fc3335a36f5f845c48aedd5a518f8cd7088be4fe4f07d2dc5f57ceb21fc82e</t>
+          <t>cc42793d0e11c2a2388e9619b931c98d68f8e80406163f2c53c61dc57e6fc887</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
@@ -12165,12 +12165,12 @@
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>2f506933e53d4088dd8749f03e16f6dd90fe7aa3cad70d5560dead55bce636b4</t>
+          <t>e8652df525d1bef5b22128f49213e4cdb58dfff0e3df073951e24de900a3c79b</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>2f4a979bae33bcce2c2179513dfc3d1c974c50e90c8f02f4df549494e4c7d5b7</t>
+          <t>5a9b713701fdf68de784ef62f8cbb1106ac2fe738ef811e696c57d9301c5d4a7</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>0a40b3b4ca763161c78781c6b9522dddf8a2b48e3965e6db0e4817470fed54c0</t>
+          <t>85dc05328b0ff2c7038af1f759b80c845a21c104ca7636ebcc82d739805ff3b3</t>
         </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
@@ -12939,12 +12939,12 @@
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>e82175e1024da4745a2c82daf874ada467f8a59d3d4d84c9c1e5c94ee177d15e</t>
+          <t>464f7786139248fa5b2cb3e89d7a51222825ed4aa7bc0b9d7be5ffe821f23512</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
@@ -13197,12 +13197,12 @@
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>5007ab081cdfed50fe1d489398cf57aab97f2ccbfce17fabc9919259a2ad55ce</t>
+          <t>9150068270062e89426a08ddec5408f0fe003aa10492e8e28eef704211858198</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
@@ -13455,12 +13455,12 @@
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>d42329eb3c807c43e2957bc6a44fc27a61d3968fd9d791a6340f5b7c8d733f6b</t>
+          <t>088714e57b1bd87241cf1c125c1bbd5e7fbf02d18d8c8423fec3b5c535d89043</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
@@ -13713,12 +13713,12 @@
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>be78e486313eb1955fcd18697ca2d9e5d7cd1b11a1217294e732eb8b800ca41e</t>
+          <t>8c855dca876aa02edcdeaab375e691a433322ebd653d6eeab01863d660fad72d</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
@@ -13971,12 +13971,12 @@
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>d38a44ebbb326c068ec48cf7c06ee834c63bfddc2ed011db46a2a539d467fd21</t>
+          <t>e75b228af0388ce9308ade9ec3a316fdccb22ac73ed65a839f2f73e224714f01</t>
         </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>1837f51c6b9295ee9a44d7657205379308139e9e395acae8d39ab051c4c53d33</t>
+          <t>0e443b414687ee81611d1602e545f1bf0377d88fb89daf246dc581d7481c146f</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>bb1ccba4e53272bb76eb6679cf65a7c446a56a168288082acd45376167fc06b0</t>
+          <t>165af31a1f2aadb31bdac7bbc7be732a26ac1fd0235c144e70cd826b154c6973</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
@@ -14745,12 +14745,12 @@
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>2915f6da1630be58974cd2cbd175a93ea2520a7768655e29cec8a9a097c5f1a6</t>
+          <t>71fb188344562e0437e1e551af1a03f382ac498c61cbc2f56fa979664ff0a918</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>ca07b0af22afb87e67d102c8e5d21320c3bd61d28ba9d0a17c85f597bafc46d2</t>
+          <t>be91c0756e0c9f71cb481090ca4c29c2a3893f3a3237387f2ec28750c30f2194</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
@@ -15261,12 +15261,12 @@
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>5d7effec918982413ffa56255d1e8aa4f6983e9fb09bdc6929c2ac7014036e10</t>
+          <t>a924c0c0082bbaeca1d688889cebd8370998c32203f7ff6575ebde1649bfdb15</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
